--- a/data/eval/test_questions.xlsx
+++ b/data/eval/test_questions.xlsx
@@ -6,10 +6,10 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" windowWidth="19715" windowHeight="9024" tabRatio="600" firstSheet="0" activeTab="1" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="说明" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Notes" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="questions" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="选项" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="专题" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Options" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Topics" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="191029" fullCalcOnLoad="1"/>
@@ -1085,91 +1085,91 @@
     <row r="1" ht="16.8" customHeight="1">
       <c r="A1" s="5" t="inlineStr">
         <is>
-          <t>苹果病虫害 RAG 题库模板（每题一行，填写“questions”页）</t>
+          <t>Apple pest and disease RAG question bank template (one question per row, fill in the "questions" sheet)</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>1. 先在原文中定位事实，再写问题和参考答案；不要先问模型再把模型答案当参考答案。</t>
+          <t>1. Locate the facts in the source first, then write the question and reference answer; never use a model answer as the reference answer.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2. 每题 3–5 个必答要点，评分 0–4 分对照这些要点。</t>
+          <t>2. Each question has 3–5 required points; the 0–4 score is given against these points.</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>3. chunk_ids 填数据库片段 ID（可在问答页证据卡或 web_chunks_reviewed.json 查找）；check 命令会核对其存在。</t>
+          <t>3. chunk_ids are database chunk IDs (see the evidence cards in the Q&amp;A page or web_chunks_reviewed.json); the check command verifies that they exist.</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>4. 开发集与测试集按专题和问题类型分开，不要把同一问题改写后放进两组。</t>
+          <t>4. Keep the development and test sets apart by topic and question type; never put a rewritten version of the same question in both.</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>5. 参考答案须由另一名成员复核，复核通过后 status 改为 reviewed。冻结前运行：python 代码/tools/question_bank.py check 文件.xlsx --export</t>
+          <t>5. Another member must review each reference answer; after review set status to reviewed. Before freezing run: python code/tools/question_bank.py check FILE.xlsx --export</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>6. 被测系统只能收到 question_en；参考答案和评分标准不得进入提示词。</t>
+          <t>6. The tested system receives only question_en; reference answers and scoring criteria never enter the prompt.</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>7. 示例行 D001、D002 正式填写前删除。</t>
+          <t>7. Delete example rows D001 and D002 before use.</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>计划配额（测试集 50 题，按问法）：</t>
+          <t>Planned quota (test set, 50 questions, by style):</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t xml:space="preserve">   农户口吻: 35</t>
+          <t xml:space="preserve">   Farmer's voice: 35</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t xml:space="preserve">   附带地区/环境: 10</t>
+          <t xml:space="preserve">   With region or environment context: 10</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t xml:space="preserve">   偏僻专题: 5</t>
+          <t xml:space="preserve">   Rare topic: 5</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>（问法写在 notes 开头：农户口吻 / 附带地区/环境 / 偏僻专题）</t>
+          <t>(Write the style at the start of notes: Farmer's voice / With region or environment context / Rare topic)</t>
         </is>
       </c>
     </row>
@@ -1311,7 +1311,7 @@
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>D001–D020 开发集；T001–T060 测试集，唯一且不复用</t>
+          <t>D001–D020 development set; T001–T060 test set; unique and never reused</t>
         </is>
       </c>
       <c r="B2" s="3" t="inlineStr">
@@ -1321,77 +1321,77 @@
       </c>
       <c r="C2" s="3" t="inlineStr">
         <is>
-          <t>范围表编号 T01–T46，见“专题”页</t>
+          <t>Scope table identifier T01–T46, see the "Topics" sheet</t>
         </is>
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>见“选项”页</t>
+          <t>See the "Options" sheet</t>
         </is>
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>证据所属地区，如 United States - Pacific Northwest / New Zealand</t>
+          <t>Region of the evidence, e.g. United States - Pacific Northwest / New Zealand</t>
         </is>
       </c>
       <c r="F2" s="3" t="inlineStr">
         <is>
-          <t>生育/采后阶段</t>
+          <t>Growth or postharvest stage</t>
         </is>
       </c>
       <c r="G2" s="3" t="inlineStr">
         <is>
-          <t>answerable / partial / unanswerable（语料内）</t>
+          <t>answerable / partial / unanswerable (within the corpus)</t>
         </is>
       </c>
       <c r="H2" s="3" t="inlineStr">
         <is>
-          <t>英文问题；写明地区或来源情境，不出现答案线索</t>
+          <t>Question in English; state region or source context; no answer hints</t>
         </is>
       </c>
       <c r="I2" s="3" t="inlineStr">
         <is>
-          <t>只依据所引原文写成的参考答案</t>
+          <t>Reference answer written only from the cited passages</t>
         </is>
       </c>
       <c r="J2" s="3" t="inlineStr">
         <is>
-          <t>3–5 个必答要点，用 | 分隔；评分 0–4 依据</t>
+          <t>3–5 required points separated by |; basis for the 0–4 score</t>
         </is>
       </c>
       <c r="K2" s="3" t="inlineStr">
         <is>
-          <t>判为重大错误的情形，用 | 分隔</t>
+          <t>Cases counted as major errors, separated by |</t>
         </is>
       </c>
       <c r="L2" s="3" t="inlineStr">
         <is>
-          <t>边界题：可答部分 / 应拒答部分 / 理由</t>
+          <t>Boundary questions: answerable part / part to decline / reason</t>
         </is>
       </c>
       <c r="M2" s="3" t="inlineStr">
         <is>
-          <t>如 S001|S036</t>
+          <t>e.g. S001|S036</t>
         </is>
       </c>
       <c r="N2" s="3" t="inlineStr">
         <is>
-          <t>如 S001:web:3|S001:web:4（可用多个等价片段）</t>
+          <t>e.g. S001:web:3|S001:web:4 (several equivalent chunks allowed)</t>
         </is>
       </c>
       <c r="O2" s="3" t="inlineStr">
         <is>
-          <t>PDF 页码或网页章节，如 p.12 / Symptoms and Signs</t>
+          <t>PDF page or web section, e.g. p.12 / Symptoms and Signs</t>
         </is>
       </c>
       <c r="P2" s="3" t="inlineStr">
         <is>
-          <t>出题人</t>
+          <t>Author</t>
         </is>
       </c>
       <c r="Q2" s="3" t="inlineStr">
         <is>
-          <t>复核人，必须不同于出题人</t>
+          <t>Reviewer; must differ from the author</t>
         </is>
       </c>
       <c r="R2" s="3" t="inlineStr">
@@ -1401,12 +1401,12 @@
       </c>
       <c r="S2" s="3" t="inlineStr">
         <is>
-          <t>从 1 开始，修改后加 1</t>
+          <t>Starts at 1; add 1 after each change</t>
         </is>
       </c>
       <c r="T2" s="3" t="inlineStr">
         <is>
-          <t>争议、地区转用、来源冲突等</t>
+          <t>Disputes, regional transfer, source conflicts, etc.</t>
         </is>
       </c>
     </row>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="T3" s="4" t="inlineStr">
         <is>
-          <t>农户口吻 v1; 提问者未说明地区；地区性数值须注明来源; Evidence check 2026-10-16: missing citation: added S001:web:26 for green-tip timing</t>
+          <t>Farmer's voice v1; region not stated by the asker; regional values must state their source; Evidence check 2026-10-16: missing citation: added S001:web:26 for green-tip timing</t>
         </is>
       </c>
     </row>
@@ -1598,7 +1598,7 @@
       </c>
       <c r="T4" s="4" t="inlineStr">
         <is>
-          <t>农户口吻 v1; 提问者未说明地区；地区性数值须注明来源; Evidence check 2026-10-16: all statements and numbers traced to cited chunks.</t>
+          <t>Farmer's voice v1; region not stated by the asker; regional values must state their source; Evidence check 2026-10-16: all statements and numbers traced to cited chunks.</t>
         </is>
       </c>
     </row>
@@ -1694,7 +1694,7 @@
       </c>
       <c r="T5" s="4" t="inlineStr">
         <is>
-          <t>农户口吻 v1; 提问者未说明地区；地区性数值须注明来源; Evidence check 2026-10-16: missing citation: added S251:web:2 for hand-lens check</t>
+          <t>Farmer's voice v1; region not stated by the asker; regional values must state their source; Evidence check 2026-10-16: missing citation: added S251:web:2 for hand-lens check</t>
         </is>
       </c>
     </row>
@@ -1790,7 +1790,7 @@
       </c>
       <c r="T6" s="4" t="inlineStr">
         <is>
-          <t>农户口吻 v1; 提问者未说明地区；地区性数值须注明来源; Evidence check 2026-10-16: all statements and numbers traced to cited chunks.</t>
+          <t>Farmer's voice v1; region not stated by the asker; regional values must state their source; Evidence check 2026-10-16: all statements and numbers traced to cited chunks.</t>
         </is>
       </c>
     </row>
@@ -1886,7 +1886,7 @@
       </c>
       <c r="T7" s="4" t="inlineStr">
         <is>
-          <t>农户口吻 v1; 提问者未说明地区；地区性数值须注明来源; Evidence check 2026-10-16: all statements and numbers traced to cited chunks.</t>
+          <t>Farmer's voice v1; region not stated by the asker; regional values must state their source; Evidence check 2026-10-16: all statements and numbers traced to cited chunks.</t>
         </is>
       </c>
     </row>
@@ -1982,7 +1982,7 @@
       </c>
       <c r="T8" s="4" t="inlineStr">
         <is>
-          <t>农户口吻 v1; 提问者未说明地区；地区性数值须注明来源; Evidence check 2026-10-16: all statements and numbers traced to cited chunks.</t>
+          <t>Farmer's voice v1; region not stated by the asker; regional values must state their source; Evidence check 2026-10-16: all statements and numbers traced to cited chunks.</t>
         </is>
       </c>
     </row>
@@ -2078,7 +2078,7 @@
       </c>
       <c r="T9" s="4" t="inlineStr">
         <is>
-          <t>农户口吻 v1; 提问者未说明地区；地区性数值须注明来源; Evidence check 2026-10-16: all statements and numbers traced to cited chunks.</t>
+          <t>Farmer's voice v1; region not stated by the asker; regional values must state their source; Evidence check 2026-10-16: all statements and numbers traced to cited chunks.</t>
         </is>
       </c>
     </row>
@@ -2174,7 +2174,7 @@
       </c>
       <c r="T10" s="4" t="inlineStr">
         <is>
-          <t>农户口吻 v1; 提问者未说明地区；地区性数值须注明来源; Evidence check 2026-10-16: all statements and numbers traced to cited chunks.</t>
+          <t>Farmer's voice v1; region not stated by the asker; regional values must state their source; Evidence check 2026-10-16: all statements and numbers traced to cited chunks.</t>
         </is>
       </c>
     </row>
@@ -2270,7 +2270,7 @@
       </c>
       <c r="T11" s="4" t="inlineStr">
         <is>
-          <t>农户口吻 v1; 提问者未说明地区；地区性数值须注明来源; Evidence check 2026-10-16: all statements and numbers traced to cited chunks.</t>
+          <t>Farmer's voice v1; region not stated by the asker; regional values must state their source; Evidence check 2026-10-16: all statements and numbers traced to cited chunks.</t>
         </is>
       </c>
     </row>
@@ -2366,7 +2366,7 @@
       </c>
       <c r="T12" s="4" t="inlineStr">
         <is>
-          <t>农户口吻 v1; 提问者未说明地区；地区性数值须注明来源; Evidence check 2026-10-16: all statements and numbers traced to cited chunks.</t>
+          <t>Farmer's voice v1; region not stated by the asker; regional values must state their source; Evidence check 2026-10-16: all statements and numbers traced to cited chunks.</t>
         </is>
       </c>
     </row>
@@ -2462,7 +2462,7 @@
       </c>
       <c r="T13" s="4" t="inlineStr">
         <is>
-          <t>农户口吻 v1; 提问者未说明地区；地区性数值须注明来源; Evidence check 2026-10-16: all statements and numbers traced to cited chunks.</t>
+          <t>Farmer's voice v1; region not stated by the asker; regional values must state their source; Evidence check 2026-10-16: all statements and numbers traced to cited chunks.</t>
         </is>
       </c>
     </row>
@@ -2558,7 +2558,7 @@
       </c>
       <c r="T14" s="4" t="inlineStr">
         <is>
-          <t>农户口吻 v1; 提问者未说明地区；地区性数值须注明来源; Evidence check 2026-10-16: all statements and numbers traced to cited chunks.</t>
+          <t>Farmer's voice v1; region not stated by the asker; regional values must state their source; Evidence check 2026-10-16: all statements and numbers traced to cited chunks.</t>
         </is>
       </c>
     </row>
@@ -2654,7 +2654,7 @@
       </c>
       <c r="T15" s="4" t="inlineStr">
         <is>
-          <t>农户口吻 v1; 提问者未说明地区；地区性数值须注明来源; Evidence check 2026-10-16: all statements and numbers traced to cited chunks.</t>
+          <t>Farmer's voice v1; region not stated by the asker; regional values must state their source; Evidence check 2026-10-16: all statements and numbers traced to cited chunks.</t>
         </is>
       </c>
     </row>
@@ -2750,7 +2750,7 @@
       </c>
       <c r="T16" s="4" t="inlineStr">
         <is>
-          <t>农户口吻 v1; 提问者未说明地区；地区性数值须注明来源; Evidence check 2026-10-16: all statements and numbers traced to cited chunks.</t>
+          <t>Farmer's voice v1; region not stated by the asker; regional values must state their source; Evidence check 2026-10-16: all statements and numbers traced to cited chunks.</t>
         </is>
       </c>
     </row>
@@ -2846,7 +2846,7 @@
       </c>
       <c r="T17" s="4" t="inlineStr">
         <is>
-          <t>农户口吻 v1; 提问者未说明地区；地区性数值须注明来源; Evidence check 2026-10-16: all statements and numbers traced to cited chunks.</t>
+          <t>Farmer's voice v1; region not stated by the asker; regional values must state their source; Evidence check 2026-10-16: all statements and numbers traced to cited chunks.</t>
         </is>
       </c>
     </row>
@@ -2942,7 +2942,7 @@
       </c>
       <c r="T18" s="4" t="inlineStr">
         <is>
-          <t>农户口吻 v1; 提问者未说明地区；地区性数值须注明来源; Evidence check 2026-10-16: missing citation: added S072:web:2 (fiddle-string) and S072:web:5 (fungicides with pruning)</t>
+          <t>Farmer's voice v1; region not stated by the asker; regional values must state their source; Evidence check 2026-10-16: missing citation: added S072:web:2 (fiddle-string) and S072:web:5 (fungicides with pruning)</t>
         </is>
       </c>
     </row>
@@ -3038,7 +3038,7 @@
       </c>
       <c r="T19" s="4" t="inlineStr">
         <is>
-          <t>农户口吻 v1; 提问者未说明地区；地区性数值须注明来源; Evidence check 2026-10-16: all statements and numbers traced to cited chunks.</t>
+          <t>Farmer's voice v1; region not stated by the asker; regional values must state their source; Evidence check 2026-10-16: all statements and numbers traced to cited chunks.</t>
         </is>
       </c>
     </row>
@@ -3134,7 +3134,7 @@
       </c>
       <c r="T20" s="4" t="inlineStr">
         <is>
-          <t>农户口吻 v1; 提问者未说明地区；地区性数值须注明来源; Evidence check 2026-10-16: missing citation: added S073:web:5 (nematode-free trees) and S073:web:18 (fumigation)</t>
+          <t>Farmer's voice v1; region not stated by the asker; regional values must state their source; Evidence check 2026-10-16: missing citation: added S073:web:5 (nematode-free trees) and S073:web:18 (fumigation)</t>
         </is>
       </c>
     </row>
@@ -3230,7 +3230,7 @@
       </c>
       <c r="T21" s="4" t="inlineStr">
         <is>
-          <t>农户口吻 v1; 提问者未说明地区；地区性数值须注明来源; Evidence check 2026-10-16: all statements and numbers traced to cited chunks.</t>
+          <t>Farmer's voice v1; region not stated by the asker; regional values must state their source; Evidence check 2026-10-16: all statements and numbers traced to cited chunks.</t>
         </is>
       </c>
     </row>
@@ -3326,7 +3326,7 @@
       </c>
       <c r="T22" s="4" t="inlineStr">
         <is>
-          <t>农户口吻 v1; 提问者未说明地区；地区性数值须注明来源; Evidence check 2026-10-16: all statements and numbers traced to cited chunks.</t>
+          <t>Farmer's voice v1; region not stated by the asker; regional values must state their source; Evidence check 2026-10-16: all statements and numbers traced to cited chunks.</t>
         </is>
       </c>
     </row>
@@ -3422,7 +3422,7 @@
       </c>
       <c r="T23" s="4" t="inlineStr">
         <is>
-          <t>农户口吻 v1; 提问者未说明地区；地区性数值须注明来源; Evidence check 2026-10-16: all statements and numbers traced to cited chunks.</t>
+          <t>Farmer's voice v1; region not stated by the asker; regional values must state their source; Evidence check 2026-10-16: all statements and numbers traced to cited chunks.</t>
         </is>
       </c>
     </row>
@@ -3520,7 +3520,7 @@
       </c>
       <c r="T24" s="4" t="inlineStr">
         <is>
-          <t>农户口吻 v1; 提问者未说明地区；地区性数值须注明来源; Evidence check 2026-10-16: all statements and numbers traced to cited chunks.</t>
+          <t>Farmer's voice v1; region not stated by the asker; regional values must state their source; Evidence check 2026-10-16: all statements and numbers traced to cited chunks.</t>
         </is>
       </c>
     </row>
@@ -3616,7 +3616,7 @@
       </c>
       <c r="T25" s="4" t="inlineStr">
         <is>
-          <t>农户口吻 v1; 提问者未说明地区；地区性数值须注明来源; Evidence check 2026-10-16: all statements and numbers traced to cited chunks.</t>
+          <t>Farmer's voice v1; region not stated by the asker; regional values must state their source; Evidence check 2026-10-16: all statements and numbers traced to cited chunks.</t>
         </is>
       </c>
     </row>
@@ -3712,7 +3712,7 @@
       </c>
       <c r="T26" s="4" t="inlineStr">
         <is>
-          <t>农户口吻 v1; 提问者未说明地区；地区性数值须注明来源; Evidence check 2026-10-16: all statements and numbers traced to cited chunks.</t>
+          <t>Farmer's voice v1; region not stated by the asker; regional values must state their source; Evidence check 2026-10-16: all statements and numbers traced to cited chunks.</t>
         </is>
       </c>
     </row>
@@ -3808,7 +3808,7 @@
       </c>
       <c r="T27" s="4" t="inlineStr">
         <is>
-          <t>农户口吻 v1; 提问者未说明地区；地区性数值须注明来源; 范围表无独立果实夜蛾专题，归入 T29 卷叶蛾/食果鳞翅目类; Evidence check 2026-10-16: all statements and numbers traced to cited chunks.</t>
+          <t>Farmer's voice v1; region not stated by the asker; regional values must state their source; the scope table has no separate fruitworm topic; classified under T29 leafrollers / fruit-feeding Lepidoptera; Evidence check 2026-10-16: all statements and numbers traced to cited chunks.</t>
         </is>
       </c>
     </row>
@@ -3906,7 +3906,7 @@
       </c>
       <c r="T28" s="4" t="inlineStr">
         <is>
-          <t>农户口吻 v1; 提问者未说明地区；地区性数值须注明来源; 两来源对 M 26 说法不同，参考答案要求注明来源; Evidence check 2026-10-16: all statements and numbers traced to cited chunks.</t>
+          <t>Farmer's voice v1; region not stated by the asker; regional values must state their source; the two sources differ on M 26; the reference answer must name the source; Evidence check 2026-10-16: all statements and numbers traced to cited chunks.</t>
         </is>
       </c>
     </row>
@@ -4004,7 +4004,7 @@
       </c>
       <c r="T29" s="4" t="inlineStr">
         <is>
-          <t>农户口吻 v1; 提问者未说明地区；地区性数值须注明来源; Evidence check 2026-10-16: all statements and numbers traced to cited chunks.</t>
+          <t>Farmer's voice v1; region not stated by the asker; regional values must state their source; Evidence check 2026-10-16: all statements and numbers traced to cited chunks.</t>
         </is>
       </c>
     </row>
@@ -4102,7 +4102,7 @@
       </c>
       <c r="T30" s="4" t="inlineStr">
         <is>
-          <t>农户口吻 v1; 提问者未说明地区；地区性数值须注明来源; Evidence check 2026-10-16: wording: Maryblyt was attributed to Washington; reworded model attribution</t>
+          <t>Farmer's voice v1; region not stated by the asker; regional values must state their source; Evidence check 2026-10-16: wording: Maryblyt was attributed to Washington; reworded model attribution</t>
         </is>
       </c>
     </row>
@@ -4198,7 +4198,7 @@
       </c>
       <c r="T31" s="4" t="inlineStr">
         <is>
-          <t>农户口吻 v1; 提问者未说明地区；地区性数值须注明来源; Evidence check 2026-10-16: all statements and numbers traced to cited chunks.</t>
+          <t>Farmer's voice v1; region not stated by the asker; regional values must state their source; Evidence check 2026-10-16: all statements and numbers traced to cited chunks.</t>
         </is>
       </c>
     </row>
@@ -4294,7 +4294,7 @@
       </c>
       <c r="T32" s="4" t="inlineStr">
         <is>
-          <t>农户口吻 v1; 提问者未说明地区；地区性数值须注明来源; Evidence check 2026-10-16: all statements and numbers traced to cited chunks.</t>
+          <t>Farmer's voice v1; region not stated by the asker; regional values must state their source; Evidence check 2026-10-16: all statements and numbers traced to cited chunks.</t>
         </is>
       </c>
     </row>
@@ -4390,7 +4390,7 @@
       </c>
       <c r="T33" s="4" t="inlineStr">
         <is>
-          <t>农户口吻 v1; 提问者未说明地区；地区性数值须注明来源; Evidence check 2026-10-16: all statements and numbers traced to cited chunks.</t>
+          <t>Farmer's voice v1; region not stated by the asker; regional values must state their source; Evidence check 2026-10-16: all statements and numbers traced to cited chunks.</t>
         </is>
       </c>
     </row>
@@ -4452,7 +4452,7 @@
       </c>
       <c r="L34" s="4" t="inlineStr">
         <is>
-          <t>可答：网眼形状研究结论；应限定：无安装与逐种效果资料</t>
+          <t>Answerable: findings of the mesh-shape study; qualify: no material on installation or per-species effect</t>
         </is>
       </c>
       <c r="M34" s="4" t="inlineStr">
@@ -4490,7 +4490,7 @@
       </c>
       <c r="T34" s="4" t="inlineStr">
         <is>
-          <t>农户口吻 v1; 提问者未说明地区；地区性数值须注明来源; Evidence check 2026-10-16: all statements and numbers traced to cited chunks.</t>
+          <t>Farmer's voice v1; region not stated by the asker; regional values must state their source; Evidence check 2026-10-16: all statements and numbers traced to cited chunks.</t>
         </is>
       </c>
     </row>
@@ -4552,7 +4552,7 @@
       </c>
       <c r="L35" s="4" t="inlineStr">
         <is>
-          <t>可答：风险类别与调查背景；应限定：调查结果未收录</t>
+          <t>Answerable: risk categories and survey background; qualify: survey results not in the corpus</t>
         </is>
       </c>
       <c r="M35" s="4" t="inlineStr">
@@ -4592,7 +4592,7 @@
       </c>
       <c r="T35" s="4" t="inlineStr">
         <is>
-          <t>农户口吻 v1; 提问者未说明地区；地区性数值须注明来源; Evidence check 2026-10-16: all statements and numbers traced to cited chunks.</t>
+          <t>Farmer's voice v1; region not stated by the asker; regional values must state their source; Evidence check 2026-10-16: all statements and numbers traced to cited chunks.</t>
         </is>
       </c>
     </row>
@@ -4688,7 +4688,7 @@
       </c>
       <c r="T36" s="4" t="inlineStr">
         <is>
-          <t>农户口吻 v1; 提问者未说明地区；地区性数值须注明来源; Evidence check 2026-10-16: all statements and numbers traced to cited chunks.</t>
+          <t>Farmer's voice v1; region not stated by the asker; regional values must state their source; Evidence check 2026-10-16: all statements and numbers traced to cited chunks.</t>
         </is>
       </c>
     </row>
@@ -4784,7 +4784,7 @@
       </c>
       <c r="T37" s="4" t="inlineStr">
         <is>
-          <t>农户口吻 v1; 提问者未说明地区；地区性数值须注明来源; Evidence check 2026-10-16: all statements and numbers traced to cited chunks.</t>
+          <t>Farmer's voice v1; region not stated by the asker; regional values must state their source; Evidence check 2026-10-16: all statements and numbers traced to cited chunks.</t>
         </is>
       </c>
     </row>
@@ -4880,7 +4880,7 @@
       </c>
       <c r="T38" s="4" t="inlineStr">
         <is>
-          <t>附带地区/环境 v1; 提问者未说明地区；地区性数值须注明来源; Evidence check 2026-10-16: all statements and numbers traced to cited chunks.</t>
+          <t>With region or environment context v1; region not stated by the asker; regional values must state their source; Evidence check 2026-10-16: all statements and numbers traced to cited chunks.</t>
         </is>
       </c>
     </row>
@@ -4976,7 +4976,7 @@
       </c>
       <c r="T39" s="4" t="inlineStr">
         <is>
-          <t>附带地区/环境 v1; 提问者背景：New Zealand; 开发集原 D019 欧洲溃疡病题移至此，作为新西兰可答题; Evidence check 2026-10-16: all statements and numbers traced to cited chunks.</t>
+          <t>With region or environment context v1; asker context: New Zealand; former development question D019 on European canker moved here as an answerable New Zealand question; Evidence check 2026-10-16: all statements and numbers traced to cited chunks.</t>
         </is>
       </c>
     </row>
@@ -5072,7 +5072,7 @@
       </c>
       <c r="T40" s="4" t="inlineStr">
         <is>
-          <t>附带地区/环境 v1; 提问者背景：New Zealand; Evidence check 2026-10-16: all statements and numbers traced to cited chunks.</t>
+          <t>With region or environment context v1; asker context: New Zealand; Evidence check 2026-10-16: all statements and numbers traced to cited chunks.</t>
         </is>
       </c>
     </row>
@@ -5170,7 +5170,7 @@
       </c>
       <c r="T41" s="4" t="inlineStr">
         <is>
-          <t>附带地区/环境 v1; 提问者背景：New Zealand; Evidence check 2026-10-16: all statements and numbers traced to cited chunks.</t>
+          <t>With region or environment context v1; asker context: New Zealand; Evidence check 2026-10-16: all statements and numbers traced to cited chunks.</t>
         </is>
       </c>
     </row>
@@ -5232,7 +5232,7 @@
       </c>
       <c r="L42" s="4" t="inlineStr">
         <is>
-          <t>可答：新西兰迷向试验；应拒答：药剂与时机；理由：NZR03 未入库（见决定记录）</t>
+          <t>Answerable: New Zealand mating-disruption trial; decline: products and timing; reason: NZR03 not added to the corpus (see decision record)</t>
         </is>
       </c>
       <c r="M42" s="4" t="inlineStr">
@@ -5272,7 +5272,7 @@
       </c>
       <c r="T42" s="4" t="inlineStr">
         <is>
-          <t>附带地区/环境 v1; 提问者背景：New Zealand; Evidence check 2026-10-16: all statements and numbers traced to cited chunks.</t>
+          <t>With region or environment context v1; asker context: New Zealand; Evidence check 2026-10-16: all statements and numbers traced to cited chunks.</t>
         </is>
       </c>
     </row>
@@ -5370,7 +5370,7 @@
       </c>
       <c r="T43" s="4" t="inlineStr">
         <is>
-          <t>附带地区/环境 v1; 提问者背景：New Zealand; Evidence check 2026-10-16: all statements and numbers traced to cited chunks.</t>
+          <t>With region or environment context v1; asker context: New Zealand; Evidence check 2026-10-16: all statements and numbers traced to cited chunks.</t>
         </is>
       </c>
     </row>
@@ -5466,7 +5466,7 @@
       </c>
       <c r="T44" s="4" t="inlineStr">
         <is>
-          <t>附带地区/环境 v1; 提问者未说明地区；地区性数值须注明来源; Evidence check 2026-10-16: all statements and numbers traced to cited chunks.</t>
+          <t>With region or environment context v1; region not stated by the asker; regional values must state their source; Evidence check 2026-10-16: all statements and numbers traced to cited chunks.</t>
         </is>
       </c>
     </row>
@@ -5528,7 +5528,7 @@
       </c>
       <c r="L45" s="4" t="inlineStr">
         <is>
-          <t>全部应拒答：语料无苹果花叶病资料</t>
+          <t>Decline everything: the corpus has no apple mosaic material</t>
         </is>
       </c>
       <c r="M45" s="4" t="inlineStr"/>
@@ -5554,7 +5554,7 @@
       </c>
       <c r="T45" s="4" t="inlineStr">
         <is>
-          <t>附带地区/环境 v1; 提问者背景：New Zealand; 语料外问题，测试是否编造; Evidence check 2026-10-16: all statements and numbers traced to cited chunks.</t>
+          <t>With region or environment context v1; asker context: New Zealand; question outside the corpus, tests whether the system fabricates; Evidence check 2026-10-16: all statements and numbers traced to cited chunks.</t>
         </is>
       </c>
     </row>
@@ -5652,7 +5652,7 @@
       </c>
       <c r="T46" s="4" t="inlineStr">
         <is>
-          <t>附带地区/环境 v1; 提问者背景：New Zealand; Evidence check 2026-10-16: all statements and numbers traced to cited chunks.</t>
+          <t>With region or environment context v1; asker context: New Zealand; Evidence check 2026-10-16: all statements and numbers traced to cited chunks.</t>
         </is>
       </c>
     </row>
@@ -5714,7 +5714,7 @@
       </c>
       <c r="L47" s="4" t="inlineStr">
         <is>
-          <t>可答：信息素诱捕研究、无正式方案；应拒答：新西兰防治阈值</t>
+          <t>Answerable: pheromone trapping research, no formal protocol; decline: New Zealand control thresholds</t>
         </is>
       </c>
       <c r="M47" s="4" t="inlineStr">
@@ -5754,7 +5754,7 @@
       </c>
       <c r="T47" s="4" t="inlineStr">
         <is>
-          <t>附带地区/环境 v1; 提问者背景：New Zealand; Evidence check 2026-10-16: all statements and numbers traced to cited chunks.</t>
+          <t>With region or environment context v1; asker context: New Zealand; Evidence check 2026-10-16: all statements and numbers traced to cited chunks.</t>
         </is>
       </c>
     </row>
@@ -5850,7 +5850,7 @@
       </c>
       <c r="T48" s="4" t="inlineStr">
         <is>
-          <t>偏僻专题 v1; 提问者未说明地区；地区性数值须注明来源; Evidence check 2026-10-16: all statements and numbers traced to cited chunks.</t>
+          <t>Rare topic v1; region not stated by the asker; regional values must state their source; Evidence check 2026-10-16: all statements and numbers traced to cited chunks.</t>
         </is>
       </c>
     </row>
@@ -5946,7 +5946,7 @@
       </c>
       <c r="T49" s="4" t="inlineStr">
         <is>
-          <t>偏僻专题 v1; 提问者未说明地区；地区性数值须注明来源; Evidence check 2026-10-16: all statements and numbers traced to cited chunks.</t>
+          <t>Rare topic v1; region not stated by the asker; regional values must state their source; Evidence check 2026-10-16: all statements and numbers traced to cited chunks.</t>
         </is>
       </c>
     </row>
@@ -6008,7 +6008,7 @@
       </c>
       <c r="L50" s="4" t="inlineStr">
         <is>
-          <t>可答：新西兰温室药剂试验；应拒答：症状确认；理由：语料无 Elsinoe 症状描述</t>
+          <t>Answerable: New Zealand glasshouse product trial; decline: symptom confirmation; reason: the corpus has no description of Elsinoe symptoms</t>
         </is>
       </c>
       <c r="M50" s="4" t="inlineStr">
@@ -6046,7 +6046,7 @@
       </c>
       <c r="T50" s="4" t="inlineStr">
         <is>
-          <t>偏僻专题 v1; 提问者背景：New Zealand; Evidence check 2026-10-16: all statements and numbers traced to cited chunks. (2009 = study year from source metadata)</t>
+          <t>Rare topic v1; asker context: New Zealand; Evidence check 2026-10-16: all statements and numbers traced to cited chunks. (2009 = study year from source metadata)</t>
         </is>
       </c>
     </row>
@@ -6142,7 +6142,7 @@
       </c>
       <c r="T51" s="4" t="inlineStr">
         <is>
-          <t>偏僻专题 v1; 提问者未说明地区；地区性数值须注明来源; Evidence check 2026-10-16: all statements and numbers traced to cited chunks.</t>
+          <t>Rare topic v1; region not stated by the asker; regional values must state their source; Evidence check 2026-10-16: all statements and numbers traced to cited chunks.</t>
         </is>
       </c>
     </row>
@@ -6238,26 +6238,26 @@
       </c>
       <c r="T52" s="4" t="inlineStr">
         <is>
-          <t>偏僻专题 v1; 提问者未说明地区；地区性数值须注明来源; Evidence check 2026-10-16: all statements and numbers traced to cited chunks.</t>
+          <t>Rare topic v1; region not stated by the asker; regional values must state their source; Evidence check 2026-10-16: all statements and numbers traced to cited chunks.</t>
         </is>
       </c>
     </row>
   </sheetData>
   <dataValidations count="5">
     <dataValidation sqref="B3:B500" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>选项!$A$2:$A$3</formula1>
+      <formula1>'Options'!$A$2:$A$3</formula1>
     </dataValidation>
     <dataValidation sqref="D3:D500" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>选项!$B$2:$B$7</formula1>
+      <formula1>'Options'!$B$2:$B$7</formula1>
     </dataValidation>
     <dataValidation sqref="F3:F500" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>选项!$D$2:$D$7</formula1>
+      <formula1>'Options'!$D$2:$D$7</formula1>
     </dataValidation>
     <dataValidation sqref="G3:G500" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>选项!$C$2:$C$4</formula1>
+      <formula1>'Options'!$C$2:$C$4</formula1>
     </dataValidation>
     <dataValidation sqref="R3:R500" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>选项!$E$2:$E$5</formula1>
+      <formula1>'Options'!$E$2:$E$5</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -6467,7 +6467,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Apple scab 苹果黑星病</t>
+          <t>Apple scab</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -6489,7 +6489,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Fire blight 火疫病</t>
+          <t>Fire blight</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -6511,7 +6511,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Powdery mildew 白粉病</t>
+          <t>Powdery mildew</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -6533,7 +6533,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>European canker 欧洲溃疡病</t>
+          <t>European canker</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -6555,7 +6555,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Apple anthracnose 苹果炭疽溃疡类专题</t>
+          <t>Apple anthracnose (canker) topic</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -6577,7 +6577,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Phytophthora root/crown rot 疫霉根腐病</t>
+          <t>Phytophthora root/crown rot</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -6599,7 +6599,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Armillaria root rot 蜜环菌根腐病</t>
+          <t>Armillaria root rot</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -6621,7 +6621,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Bacterial blossom blast 细菌性花枯</t>
+          <t>Bacterial blossom blast</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -6643,7 +6643,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Black rot / Frogeye leaf spot 黑腐病</t>
+          <t>Black rot / Frogeye leaf spot</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -6665,7 +6665,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Bitter rot 苦腐病</t>
+          <t>Bitter rot</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -6687,7 +6687,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>White rot 白腐病</t>
+          <t>White rot</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -6709,7 +6709,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Sooty blotch / Flyspeck 煤污病与蝇粪病</t>
+          <t>Sooty blotch / Flyspeck</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -6731,7 +6731,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Cedar apple / Quince rust 锈病</t>
+          <t>Cedar apple / Quince rust</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -6753,7 +6753,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Blue mold 青霉病</t>
+          <t>Blue mold</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -6775,7 +6775,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Gray mold 灰霉病</t>
+          <t>Gray mold</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -6797,7 +6797,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Bull's eye rot 牛眼腐病</t>
+          <t>Bull's eye rot</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -6819,7 +6819,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Mucor rot 毛霉腐烂</t>
+          <t>Mucor rot</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -6863,7 +6863,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Marssonina blotch 苹果褐斑病</t>
+          <t>Marssonina blotch</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -6885,7 +6885,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Crown gall 根癌病</t>
+          <t>Crown gall</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -6907,7 +6907,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Core rot / Moldy core 果心腐烂</t>
+          <t>Core rot / Moldy core</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -6929,7 +6929,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Apple replant disease 连作障碍专题</t>
+          <t>Apple replant disease topic</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -6951,7 +6951,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Codling moth 苹果蠹蛾</t>
+          <t>Codling moth</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -6973,7 +6973,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Apple maggot 苹果实蝇</t>
+          <t>Apple maggot</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -6995,7 +6995,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Woolly apple aphid 苹果绵蚜</t>
+          <t>Woolly apple aphid</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -7017,7 +7017,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Green/apple/spirea aphids 苹果蚜类</t>
+          <t>Green/apple/spirea aphids</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -7083,7 +7083,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Leafrollers 卷叶蛾类</t>
+          <t>Leafrollers</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -7105,7 +7105,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Lightbrown apple moth 浅褐苹果蛾</t>
+          <t>Lightbrown apple moth</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -7122,7 +7122,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>European red mite 欧洲红蜘蛛</t>
+          <t>European red mite</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -7144,7 +7144,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Spider mites 叶螨类</t>
+          <t>Spider mites</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -7166,7 +7166,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Apple rust mite 苹果锈螨</t>
+          <t>Apple rust mite</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -7188,7 +7188,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>San Jose scale 圣何塞蚧</t>
+          <t>San Jose scale</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -7210,7 +7210,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Leafminers 潜叶蛾类</t>
+          <t>Leafminers</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -7232,7 +7232,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Leafhoppers 叶蝉类</t>
+          <t>Leafhoppers</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -7254,7 +7254,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Brown marmorated stink bug 褐斑蝽</t>
+          <t>Brown marmorated stink bug</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -7276,7 +7276,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Bronze beetle 铜色甲虫</t>
+          <t>Bronze beetle</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -7320,7 +7320,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Oriental fruit moth 东方果蛾</t>
+          <t>Oriental fruit moth</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -7342,7 +7342,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Plum curculio 李象甲</t>
+          <t>Plum curculio</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -7364,7 +7364,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Apple mosaic 苹果花叶病</t>
+          <t>Apple mosaic</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -7381,7 +7381,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Apple leafcurling midge 苹果卷叶瘿蚊</t>
+          <t>Apple leafcurling midge</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -7398,7 +7398,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Mealybugs 粉蚧类（苹果）</t>
+          <t>Mealybugs (apple)</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -7415,7 +7415,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Alternaria 相关苹果病害</t>
+          <t>Alternaria-related apple diseases</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -7432,7 +7432,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Elsinoe 相关苹果病害</t>
+          <t>Elsinoe-related apple diseases</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
